--- a/WorkBot/main/data/order_archive/Ithaca Bakery/Ithaca Bakery_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Ithaca Bakery/Ithaca Bakery_Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,154 +1437,6 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Tea Bags - English Breakfast (Twinings)</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="E56" t="n">
-        <v>9.18</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Bag - Poly (Retail Portion)</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>2</v>
-      </c>
-      <c r="D57" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="E57" t="n">
-        <v>38.58</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>PERF</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Egg Patty - Vegan</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>99.59</v>
-      </c>
-      <c r="E58" t="n">
-        <v>199.18</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Flour - Millers Choice</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Goat Cheese</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>4</v>
-      </c>
-      <c r="D60" t="n">
-        <v>22.24</v>
-      </c>
-      <c r="E60" t="n">
-        <v>88.95999999999999</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Nuts - Walnut Halves &amp; Pieces</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="E61" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Lentz</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Oats</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>43.94</v>
-      </c>
-      <c r="E62" t="n">
-        <v>43.94</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Container - HD Deli (32oz)</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>72.98999999999999</v>
-      </c>
-      <c r="E63" t="n">
-        <v>72.98999999999999</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
